--- a/data/trans_orig/P44A$endoscopia-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2012 (tasa de respuesta: 96,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,62 +1336,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1931</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7130</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>6622</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26219</t>
+          <t>26174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>33881</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18715</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26085</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23240</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>28033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22321</t>
+          <t>21827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30862</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -2669,97 +2669,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1758</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>1957</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>6926</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>12863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56432</t>
+          <t>57249</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>78039</t>
+          <t>77847</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54746</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76130</t>
+          <t>75574</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116716</t>
+          <t>117536</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>146163</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>25952</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60844</t>
+          <t>60227</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>90540</t>
+          <t>89149</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27529</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>47104</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>42309</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>69247</t>
+          <t>68700</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2016 (tasa de respuesta: 96,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,84%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>64,59%</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26695</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,62 +5218,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>8095</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7429</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37123</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53653</t>
+          <t>52653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,48%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21781</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>33636</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -6812,12 +6812,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70282</t>
+          <t>69928</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>95764</t>
+          <t>95964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>53705</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76011</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>131494</t>
+          <t>129556</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>165408</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26726</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46469</t>
+          <t>47067</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70793</t>
+          <t>71353</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>81520</t>
+          <t>79372</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>113707</t>
+          <t>113137</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47997</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>20717</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41551</t>
+          <t>40909</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>51618</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83682</t>
+          <t>82170</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2023 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52115</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72344</t>
+          <t>71272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72917</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>97381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69256</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88401</t>
+          <t>89361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46809</t>
+          <t>46906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59019</t>
+          <t>58979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120649</t>
+          <t>121051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143084</t>
+          <t>144425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28985</t>
+          <t>28031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -7923,97 +7923,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>41554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63062</t>
+          <t>62238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46459</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62266</t>
+          <t>62664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29407</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>38910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79309</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>97612</t>
+          <t>98311</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -8379,97 +8379,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1511</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127953</t>
+          <t>127581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>319566</t>
+          <t>316549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>139508</t>
+          <t>141085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>344067</t>
+          <t>345581</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198928</t>
+          <t>196053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>323308</t>
+          <t>321241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>232944</t>
+          <t>231406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351794</t>
+          <t>352437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47288</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315478</t>
+          <t>309282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334660</t>
+          <t>336161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8870,62 +8870,62 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>7727</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>8048</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55936</t>
+          <t>56805</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77541</t>
+          <t>78050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37176</t>
+          <t>37942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85571</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109940</t>
+          <t>110300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>95805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116325</t>
+          <t>116090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50995</t>
+          <t>49723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63278</t>
+          <t>62901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150875</t>
+          <t>151403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174940</t>
+          <t>175179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39298</t>
+          <t>40702</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9326,62 +9326,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3913</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>42527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51042</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69873</t>
+          <t>69522</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71562</t>
+          <t>71703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85513</t>
+          <t>85462</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>112351</t>
+          <t>113332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131642</t>
+          <t>131904</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,38%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>32306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>423</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44274</t>
+          <t>44172</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59450</t>
+          <t>60790</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>46077</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62386</t>
+          <t>62271</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76720</t>
+          <t>76499</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91178</t>
+          <t>91123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79719</t>
+          <t>79412</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94112</t>
+          <t>93412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>24366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -10203,97 +10203,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>316618</t>
+          <t>316217</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>654518</t>
+          <t>629454</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>159660</t>
+          <t>159484</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189203</t>
+          <t>188939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>486222</t>
+          <t>482184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>913465</t>
+          <t>907725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>492661</t>
+          <t>491811</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>699068</t>
+          <t>693458</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>318300</t>
+          <t>318404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>347255</t>
+          <t>347236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>829998</t>
+          <t>830030</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1073250</t>
+          <t>1072139</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99008</t>
+          <t>97042</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>596502</t>
+          <t>576780</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>43758</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>63466</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>149792</t>
+          <t>149337</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>754429</t>
+          <t>757237</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -10659,12 +10659,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44A$endoscopia-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>17181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15527</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26174</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>33993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18154</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>23107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37687</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>28723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21827</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>30006</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,19 +2980,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>987</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75574</t>
+          <t>74467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>117536</t>
+          <t>116152</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>146163</t>
+          <t>145971</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>20742</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41717</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>52413</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,82 +3709,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>47,92%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>33772</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>23835</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>44228</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>31,87%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>74842</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>60141</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>89037</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>34,76%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>27,93%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>33772</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>25952</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>44986</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>24,49%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>42,46%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>74842</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>60227</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>89149</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47104</t>
+          <t>48655</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>42190</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>70962</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,29%</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>26136</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>23939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37653</t>
+          <t>37318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>36839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52653</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20402</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33636</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6406,19 +6406,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>29760</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>29760</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -6812,12 +6812,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>69918</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>95964</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53705</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>76144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>129556</t>
+          <t>130491</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>164495</t>
+          <t>164755</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>37311</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47067</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71353</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>28013</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>79372</t>
+          <t>80892</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>113137</t>
+          <t>114136</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47921</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>40909</t>
+          <t>42127</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>83712</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -7579,32 +7579,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62150</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>55832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71272</t>
+          <t>77202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7614,32 +7614,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>19178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7649,32 +7649,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>84976</t>
+          <t>92526</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73542</t>
+          <t>80488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97381</t>
+          <t>103875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79338</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>73040</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89361</t>
+          <t>93883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7727,32 +7727,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53287</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46906</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58979</t>
+          <t>65834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7762,32 +7762,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>132625</t>
+          <t>143583</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121051</t>
+          <t>130902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144425</t>
+          <t>155470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>22214</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>31130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -8035,32 +8035,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33575</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>27502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41554</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8105,32 +8105,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>57201</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42306</t>
+          <t>47615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62238</t>
+          <t>67913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -8148,32 +8148,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>55510</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>46926</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62664</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8183,32 +8183,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29922</t>
+          <t>34162</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8218,32 +8218,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>89323</t>
+          <t>95311</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80018</t>
+          <t>84893</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98311</t>
+          <t>104619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -8491,32 +8491,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>279839</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127581</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316549</t>
+          <t>48122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8526,32 +8526,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>293166</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141085</t>
+          <t>43717</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>345581</t>
+          <t>62611</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -8604,32 +8604,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>298372</t>
+          <t>57527</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196053</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>65568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8639,32 +8639,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>30210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8674,32 +8674,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>322851</t>
+          <t>84347</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231406</t>
+          <t>74133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>352437</t>
+          <t>93566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -8717,32 +8717,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>258477</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46260</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309282</t>
+          <t>23875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8752,32 +8752,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8787,32 +8787,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>260281</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336161</t>
+          <t>26518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -8947,32 +8947,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>74293</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56805</t>
+          <t>63025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78050</t>
+          <t>86422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8982,32 +8982,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24206</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>40338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9017,32 +9017,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>96919</t>
+          <t>107968</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>93639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110300</t>
+          <t>121459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -9060,32 +9060,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>106499</t>
+          <t>115020</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95805</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116090</t>
+          <t>126324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>57201</t>
+          <t>61526</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49723</t>
+          <t>54614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62901</t>
+          <t>68244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9130,32 +9130,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>163700</t>
+          <t>176545</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151403</t>
+          <t>161717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175179</t>
+          <t>190134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -9173,32 +9173,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31783</t>
+          <t>34685</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9208,32 +9208,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>33408</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40702</t>
+          <t>42905</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -9403,32 +9403,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>34646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9438,32 +9438,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36085</t>
+          <t>38265</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9473,32 +9473,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>59625</t>
+          <t>65207</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50423</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69522</t>
+          <t>76851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -9516,32 +9516,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44302</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50287</t>
+          <t>54768</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9551,32 +9551,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>78339</t>
+          <t>85151</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71703</t>
+          <t>78043</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85462</t>
+          <t>92060</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9586,32 +9586,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>122642</t>
+          <t>133263</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>113332</t>
+          <t>121461</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131904</t>
+          <t>142787</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -9629,32 +9629,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9664,32 +9664,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>24354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9699,32 +9699,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32306</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>609</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9777,32 +9777,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9812,39 +9812,39 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9894,32 +9894,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52352</t>
+          <t>57815</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44172</t>
+          <t>49210</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60790</t>
+          <t>65955</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>53947</t>
+          <t>59429</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46077</t>
+          <t>50599</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62271</t>
+          <t>69119</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -9972,27 +9972,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10007,32 +10007,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>84361</t>
+          <t>93460</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76499</t>
+          <t>85030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91123</t>
+          <t>100500</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10042,32 +10042,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>87236</t>
+          <t>96285</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79412</t>
+          <t>87350</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93412</t>
+          <t>103358</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -10120,32 +10120,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24366</t>
+          <t>27397</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10155,32 +10155,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>27473</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -10315,32 +10315,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>467419</t>
+          <t>244162</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>316217</t>
+          <t>222049</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>629454</t>
+          <t>265783</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10350,17 +10350,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>173940</t>
+          <t>191835</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>159484</t>
+          <t>175819</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188939</t>
+          <t>210647</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10385,32 +10385,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>641359</t>
+          <t>435997</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>482184</t>
+          <t>411071</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>907725</t>
+          <t>465325</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -10428,32 +10428,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>586037</t>
+          <t>363080</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>491811</t>
+          <t>341212</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>693458</t>
+          <t>383738</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10463,32 +10463,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>332340</t>
+          <t>366253</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>318404</t>
+          <t>350082</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>347236</t>
+          <t>381415</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10498,32 +10498,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>918377</t>
+          <t>729332</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>830030</t>
+          <t>702705</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1072139</t>
+          <t>754963</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -10541,32 +10541,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97042</t>
+          <t>61808</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>576780</t>
+          <t>91046</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10576,32 +10576,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>53192</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>49944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63466</t>
+          <t>72705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10611,32 +10611,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>369161</t>
+          <t>136875</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>149337</t>
+          <t>118470</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>757237</t>
+          <t>156912</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -10654,32 +10654,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10689,32 +10689,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10724,32 +10724,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
